--- a/backend/tests/fixtures/validos.xlsx
+++ b/backend/tests/fixtures/validos.xlsx
@@ -444,7 +444,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>7861234567898</t>
+          <t>9780306406157</t>
         </is>
       </c>
     </row>
